--- a/Project Outline - CURRENT (1).xlsx
+++ b/Project Outline - CURRENT (1).xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resbank-my.sharepoint.com/personal/cathy_hlungwani_resbank_co_za/Documents/Documents/1. MEng - Data Science/1. Project_2025/Data/factor_timing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F6D8717-30CB-437C-9249-EFC082CAFDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{3F6D8717-30CB-437C-9249-EFC082CAFDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F74389C-03A2-4D74-8C37-9DF3B1F425F9}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" activeTab="3" xr2:uid="{290BD4F1-9242-E74E-B9AE-9AF768149F60}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{290BD4F1-9242-E74E-B9AE-9AF768149F60}"/>
   </bookViews>
   <sheets>
     <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
     <sheet name="Data Inputs" sheetId="3" r:id="rId2"/>
     <sheet name="MissingData" sheetId="5" r:id="rId3"/>
-    <sheet name="Feature Engineering" sheetId="4" r:id="rId4"/>
-    <sheet name="Model Training Procedure" sheetId="2" r:id="rId5"/>
+    <sheet name="Feature Engineering (2)" sheetId="6" r:id="rId4"/>
+    <sheet name="Feature Engineering" sheetId="4" r:id="rId5"/>
+    <sheet name="Model Training Procedure" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="534">
   <si>
     <t xml:space="preserve">Data Collection </t>
   </si>
@@ -2655,6 +2656,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2664,6 +2686,12 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2673,9 +2701,6 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2691,15 +2716,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2709,19 +2725,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2730,15 +2743,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2759,9 +2763,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3887,13 +3888,13 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="131" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="132" t="s">
         <v>532</v>
       </c>
-      <c r="D3" s="143" t="s">
+      <c r="D3" s="132" t="s">
         <v>140</v>
       </c>
       <c r="E3" s="47" t="s">
@@ -3916,9 +3917,9 @@
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="137"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
       <c r="E4" s="47" t="s">
         <v>147</v>
       </c>
@@ -3937,9 +3938,9 @@
       </c>
     </row>
     <row r="5" spans="2:10" ht="75" customHeight="1">
-      <c r="B5" s="137"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
+      <c r="B5" s="131"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
       <c r="E5" s="47" t="s">
         <v>151</v>
       </c>
@@ -3958,9 +3959,9 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="108.5">
-      <c r="B6" s="137"/>
-      <c r="C6" s="143"/>
-      <c r="D6" s="145" t="s">
+      <c r="B6" s="131"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="134" t="s">
         <v>155</v>
       </c>
       <c r="E6" s="54" t="s">
@@ -3981,9 +3982,9 @@
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="137"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
       <c r="E7" s="47" t="s">
         <v>158</v>
       </c>
@@ -4002,9 +4003,9 @@
       <c r="J7" s="52"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="137"/>
-      <c r="C8" s="143"/>
-      <c r="D8" s="145" t="s">
+      <c r="B8" s="131"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="134" t="s">
         <v>163</v>
       </c>
       <c r="E8" s="54" t="s">
@@ -4025,9 +4026,9 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="137"/>
-      <c r="C9" s="143"/>
-      <c r="D9" s="143"/>
+      <c r="B9" s="131"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
       <c r="E9" s="47" t="s">
         <v>168</v>
       </c>
@@ -4048,9 +4049,9 @@
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="137"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
       <c r="E10" s="47" t="s">
         <v>172</v>
       </c>
@@ -4069,9 +4070,9 @@
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="137"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
       <c r="E11" s="56" t="s">
         <v>174</v>
       </c>
@@ -4090,11 +4091,11 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="31">
-      <c r="B12" s="137"/>
-      <c r="C12" s="149" t="s">
+      <c r="B12" s="131"/>
+      <c r="C12" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="131" t="s">
+      <c r="D12" s="138" t="s">
         <v>176</v>
       </c>
       <c r="E12" s="57" t="s">
@@ -4115,9 +4116,9 @@
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="137"/>
-      <c r="C13" s="150"/>
-      <c r="D13" s="132"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="136"/>
+      <c r="D13" s="139"/>
       <c r="E13" s="34" t="s">
         <v>179</v>
       </c>
@@ -4136,9 +4137,9 @@
       </c>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="137"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="133"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="140"/>
       <c r="E14" s="61" t="s">
         <v>181</v>
       </c>
@@ -4157,9 +4158,9 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="46.5">
-      <c r="B15" s="137"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="131" t="s">
+      <c r="B15" s="131"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="138" t="s">
         <v>183</v>
       </c>
       <c r="E15" s="57" t="s">
@@ -4180,9 +4181,9 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="46.5">
-      <c r="B16" s="137"/>
-      <c r="C16" s="150"/>
-      <c r="D16" s="132"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="139"/>
       <c r="E16" s="34" t="s">
         <v>179</v>
       </c>
@@ -4201,9 +4202,9 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="46.5">
-      <c r="B17" s="137"/>
-      <c r="C17" s="150"/>
-      <c r="D17" s="133"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="140"/>
       <c r="E17" s="61" t="s">
         <v>181</v>
       </c>
@@ -4222,9 +4223,9 @@
       </c>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="137"/>
-      <c r="C18" s="150"/>
-      <c r="D18" s="131" t="s">
+      <c r="B18" s="131"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="138" t="s">
         <v>186</v>
       </c>
       <c r="E18" s="57" t="s">
@@ -4245,9 +4246,9 @@
       </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="137"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="132"/>
+      <c r="B19" s="131"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="139"/>
       <c r="E19" s="34" t="s">
         <v>189</v>
       </c>
@@ -4266,9 +4267,9 @@
       </c>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="137"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="133"/>
+      <c r="B20" s="131"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="140"/>
       <c r="E20" s="61" t="s">
         <v>191</v>
       </c>
@@ -4287,8 +4288,8 @@
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="137"/>
-      <c r="C21" s="151"/>
+      <c r="B21" s="131"/>
+      <c r="C21" s="137"/>
       <c r="D21" s="63" t="s">
         <v>193</v>
       </c>
@@ -4310,8 +4311,8 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="62">
-      <c r="B22" s="137"/>
-      <c r="C22" s="152" t="s">
+      <c r="B22" s="131"/>
+      <c r="C22" s="141" t="s">
         <v>196</v>
       </c>
       <c r="D22" s="64" t="s">
@@ -4335,8 +4336,8 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="62.5" thickBot="1">
-      <c r="B23" s="137"/>
-      <c r="C23" s="153"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="142"/>
       <c r="D23" s="71" t="s">
         <v>201</v>
       </c>
@@ -4358,13 +4359,13 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="31">
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="145" t="s">
         <v>205</v>
       </c>
-      <c r="C24" s="139" t="s">
+      <c r="C24" s="147" t="s">
         <v>206</v>
       </c>
-      <c r="D24" s="142" t="s">
+      <c r="D24" s="150" t="s">
         <v>140</v>
       </c>
       <c r="E24" s="75" t="s">
@@ -4387,9 +4388,9 @@
       </c>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="137"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="143"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="132"/>
       <c r="E25" s="47" t="s">
         <v>210</v>
       </c>
@@ -4410,9 +4411,9 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="31">
-      <c r="B26" s="137"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="143"/>
+      <c r="B26" s="131"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="132"/>
       <c r="E26" s="47" t="s">
         <v>214</v>
       </c>
@@ -4433,9 +4434,9 @@
       </c>
     </row>
     <row r="27" spans="2:10" ht="31">
-      <c r="B27" s="137"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="143"/>
+      <c r="B27" s="131"/>
+      <c r="C27" s="148"/>
+      <c r="D27" s="132"/>
       <c r="E27" s="47" t="s">
         <v>216</v>
       </c>
@@ -4456,9 +4457,9 @@
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="137"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="143"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="148"/>
+      <c r="D28" s="132"/>
       <c r="E28" s="47" t="s">
         <v>218</v>
       </c>
@@ -4477,9 +4478,9 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="31">
-      <c r="B29" s="137"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="144"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="148"/>
+      <c r="D29" s="133"/>
       <c r="E29" s="56" t="s">
         <v>220</v>
       </c>
@@ -4498,9 +4499,9 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="46.5">
-      <c r="B30" s="137"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="145" t="s">
+      <c r="B30" s="131"/>
+      <c r="C30" s="148"/>
+      <c r="D30" s="134" t="s">
         <v>155</v>
       </c>
       <c r="E30" s="54" t="s">
@@ -4521,9 +4522,9 @@
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="137"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="143"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="132"/>
       <c r="E31" s="47" t="s">
         <v>224</v>
       </c>
@@ -4542,9 +4543,9 @@
       <c r="J31" s="52"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="137"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="145" t="s">
+      <c r="B32" s="131"/>
+      <c r="C32" s="148"/>
+      <c r="D32" s="134" t="s">
         <v>163</v>
       </c>
       <c r="E32" s="81" t="s">
@@ -4565,9 +4566,9 @@
       </c>
     </row>
     <row r="33" spans="2:10">
-      <c r="B33" s="137"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="143"/>
+      <c r="B33" s="131"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="132"/>
       <c r="E33" s="47" t="s">
         <v>231</v>
       </c>
@@ -4586,9 +4587,9 @@
       <c r="J33" s="52"/>
     </row>
     <row r="34" spans="2:10" ht="31">
-      <c r="B34" s="137"/>
-      <c r="C34" s="141"/>
-      <c r="D34" s="144"/>
+      <c r="B34" s="131"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="133"/>
       <c r="E34" s="56" t="s">
         <v>233</v>
       </c>
@@ -4607,9 +4608,9 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="31">
-      <c r="B35" s="137"/>
+      <c r="B35" s="131"/>
       <c r="C35" s="80"/>
-      <c r="D35" s="145" t="s">
+      <c r="D35" s="134" t="s">
         <v>235</v>
       </c>
       <c r="E35" s="47" t="s">
@@ -4630,9 +4631,9 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="62">
-      <c r="B36" s="137"/>
+      <c r="B36" s="131"/>
       <c r="C36" s="80"/>
-      <c r="D36" s="143"/>
+      <c r="D36" s="132"/>
       <c r="E36" s="47" t="s">
         <v>238</v>
       </c>
@@ -4651,9 +4652,9 @@
       </c>
     </row>
     <row r="37" spans="2:10">
-      <c r="B37" s="137"/>
+      <c r="B37" s="131"/>
       <c r="C37" s="80"/>
-      <c r="D37" s="143"/>
+      <c r="D37" s="132"/>
       <c r="E37" s="47" t="s">
         <v>240</v>
       </c>
@@ -4672,9 +4673,9 @@
       </c>
     </row>
     <row r="38" spans="2:10">
-      <c r="B38" s="137"/>
+      <c r="B38" s="131"/>
       <c r="C38" s="80"/>
-      <c r="D38" s="144"/>
+      <c r="D38" s="133"/>
       <c r="E38" s="47" t="s">
         <v>243</v>
       </c>
@@ -4693,9 +4694,9 @@
       <c r="J38" s="55"/>
     </row>
     <row r="39" spans="2:10">
-      <c r="B39" s="137"/>
+      <c r="B39" s="131"/>
       <c r="C39" s="80"/>
-      <c r="D39" s="145" t="s">
+      <c r="D39" s="134" t="s">
         <v>245</v>
       </c>
       <c r="E39" s="81" t="s">
@@ -4716,9 +4717,9 @@
       </c>
     </row>
     <row r="40" spans="2:10">
-      <c r="B40" s="137"/>
+      <c r="B40" s="131"/>
       <c r="C40" s="80"/>
-      <c r="D40" s="143"/>
+      <c r="D40" s="132"/>
       <c r="E40" s="47" t="s">
         <v>248</v>
       </c>
@@ -4737,9 +4738,9 @@
       </c>
     </row>
     <row r="41" spans="2:10">
-      <c r="B41" s="137"/>
+      <c r="B41" s="131"/>
       <c r="C41" s="80"/>
-      <c r="D41" s="143"/>
+      <c r="D41" s="132"/>
       <c r="E41" s="47" t="s">
         <v>250</v>
       </c>
@@ -4758,9 +4759,9 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="93">
-      <c r="B42" s="137"/>
+      <c r="B42" s="131"/>
       <c r="C42" s="80"/>
-      <c r="D42" s="144"/>
+      <c r="D42" s="133"/>
       <c r="E42" s="47" t="s">
         <v>252</v>
       </c>
@@ -4779,11 +4780,11 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="31">
-      <c r="B43" s="137"/>
-      <c r="C43" s="146" t="s">
+      <c r="B43" s="131"/>
+      <c r="C43" s="151" t="s">
         <v>175</v>
       </c>
-      <c r="D43" s="131" t="s">
+      <c r="D43" s="138" t="s">
         <v>176</v>
       </c>
       <c r="E43" s="57" t="s">
@@ -4804,9 +4805,9 @@
       </c>
     </row>
     <row r="44" spans="2:10">
-      <c r="B44" s="137"/>
-      <c r="C44" s="147"/>
-      <c r="D44" s="132"/>
+      <c r="B44" s="131"/>
+      <c r="C44" s="152"/>
+      <c r="D44" s="139"/>
       <c r="E44" s="34" t="s">
         <v>256</v>
       </c>
@@ -4825,9 +4826,9 @@
       </c>
     </row>
     <row r="45" spans="2:10">
-      <c r="B45" s="137"/>
-      <c r="C45" s="147"/>
-      <c r="D45" s="133"/>
+      <c r="B45" s="131"/>
+      <c r="C45" s="152"/>
+      <c r="D45" s="140"/>
       <c r="E45" s="61" t="s">
         <v>258</v>
       </c>
@@ -4846,9 +4847,9 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="46.5">
-      <c r="B46" s="137"/>
-      <c r="C46" s="147"/>
-      <c r="D46" s="131" t="s">
+      <c r="B46" s="131"/>
+      <c r="C46" s="152"/>
+      <c r="D46" s="138" t="s">
         <v>183</v>
       </c>
       <c r="E46" s="57" t="s">
@@ -4869,9 +4870,9 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="46.5">
-      <c r="B47" s="137"/>
-      <c r="C47" s="147"/>
-      <c r="D47" s="132"/>
+      <c r="B47" s="131"/>
+      <c r="C47" s="152"/>
+      <c r="D47" s="139"/>
       <c r="E47" s="34" t="s">
         <v>256</v>
       </c>
@@ -4890,9 +4891,9 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="46.5">
-      <c r="B48" s="137"/>
-      <c r="C48" s="147"/>
-      <c r="D48" s="133"/>
+      <c r="B48" s="131"/>
+      <c r="C48" s="152"/>
+      <c r="D48" s="140"/>
       <c r="E48" s="61" t="s">
         <v>258</v>
       </c>
@@ -4911,9 +4912,9 @@
       </c>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="137"/>
-      <c r="C49" s="147"/>
-      <c r="D49" s="131" t="s">
+      <c r="B49" s="131"/>
+      <c r="C49" s="152"/>
+      <c r="D49" s="138" t="s">
         <v>261</v>
       </c>
       <c r="E49" s="61" t="s">
@@ -4934,9 +4935,9 @@
       </c>
     </row>
     <row r="50" spans="2:10">
-      <c r="B50" s="137"/>
-      <c r="C50" s="147"/>
-      <c r="D50" s="132"/>
+      <c r="B50" s="131"/>
+      <c r="C50" s="152"/>
+      <c r="D50" s="139"/>
       <c r="E50" s="61" t="s">
         <v>264</v>
       </c>
@@ -4955,9 +4956,9 @@
       </c>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="137"/>
-      <c r="C51" s="147"/>
-      <c r="D51" s="132"/>
+      <c r="B51" s="131"/>
+      <c r="C51" s="152"/>
+      <c r="D51" s="139"/>
       <c r="E51" s="61" t="s">
         <v>266</v>
       </c>
@@ -4976,9 +4977,9 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="31">
-      <c r="B52" s="137"/>
-      <c r="C52" s="147"/>
-      <c r="D52" s="133"/>
+      <c r="B52" s="131"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="140"/>
       <c r="E52" s="61" t="s">
         <v>268</v>
       </c>
@@ -4997,9 +4998,9 @@
       </c>
     </row>
     <row r="53" spans="2:10">
-      <c r="B53" s="137"/>
-      <c r="C53" s="147"/>
-      <c r="D53" s="131" t="s">
+      <c r="B53" s="131"/>
+      <c r="C53" s="152"/>
+      <c r="D53" s="138" t="s">
         <v>186</v>
       </c>
       <c r="E53" s="61" t="s">
@@ -5020,9 +5021,9 @@
       </c>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="137"/>
-      <c r="C54" s="147"/>
-      <c r="D54" s="133"/>
+      <c r="B54" s="131"/>
+      <c r="C54" s="152"/>
+      <c r="D54" s="140"/>
       <c r="E54" s="61" t="s">
         <v>272</v>
       </c>
@@ -5041,9 +5042,9 @@
       </c>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="137"/>
-      <c r="C55" s="147"/>
-      <c r="D55" s="131" t="s">
+      <c r="B55" s="131"/>
+      <c r="C55" s="152"/>
+      <c r="D55" s="138" t="s">
         <v>274</v>
       </c>
       <c r="E55" s="61" t="s">
@@ -5064,9 +5065,9 @@
       </c>
     </row>
     <row r="56" spans="2:10">
-      <c r="B56" s="137"/>
-      <c r="C56" s="147"/>
-      <c r="D56" s="132"/>
+      <c r="B56" s="131"/>
+      <c r="C56" s="152"/>
+      <c r="D56" s="139"/>
       <c r="E56" s="61" t="s">
         <v>277</v>
       </c>
@@ -5085,9 +5086,9 @@
       </c>
     </row>
     <row r="57" spans="2:10">
-      <c r="B57" s="137"/>
-      <c r="C57" s="147"/>
-      <c r="D57" s="132"/>
+      <c r="B57" s="131"/>
+      <c r="C57" s="152"/>
+      <c r="D57" s="139"/>
       <c r="E57" s="61" t="s">
         <v>279</v>
       </c>
@@ -5106,9 +5107,9 @@
       </c>
     </row>
     <row r="58" spans="2:10">
-      <c r="B58" s="137"/>
-      <c r="C58" s="147"/>
-      <c r="D58" s="133"/>
+      <c r="B58" s="131"/>
+      <c r="C58" s="152"/>
+      <c r="D58" s="140"/>
       <c r="E58" s="61" t="s">
         <v>281</v>
       </c>
@@ -5127,8 +5128,8 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="31">
-      <c r="B59" s="137"/>
-      <c r="C59" s="148"/>
+      <c r="B59" s="131"/>
+      <c r="C59" s="153"/>
       <c r="D59" s="63" t="s">
         <v>193</v>
       </c>
@@ -5150,8 +5151,8 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="62">
-      <c r="B60" s="137"/>
-      <c r="C60" s="134" t="s">
+      <c r="B60" s="131"/>
+      <c r="C60" s="143" t="s">
         <v>196</v>
       </c>
       <c r="D60" s="86" t="s">
@@ -5175,8 +5176,8 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="62.5" thickBot="1">
-      <c r="B61" s="138"/>
-      <c r="C61" s="135"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="144"/>
       <c r="D61" s="87" t="s">
         <v>197</v>
       </c>
@@ -5199,16 +5200,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B3:B23"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="C12:C21"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="C22:C23"/>
     <mergeCell ref="D49:D52"/>
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="D55:D58"/>
@@ -5223,6 +5214,16 @@
     <mergeCell ref="C43:C59"/>
     <mergeCell ref="D43:D45"/>
     <mergeCell ref="D46:D48"/>
+    <mergeCell ref="B3:B23"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C12:C21"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="C22:C23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5273,25 +5274,25 @@
       <c r="B3" s="114" t="s">
         <v>461</v>
       </c>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="154" t="s">
         <v>462</v>
       </c>
-      <c r="D3" s="156" t="s">
+      <c r="D3" s="154" t="s">
         <v>463</v>
       </c>
-      <c r="E3" s="156" t="s">
+      <c r="E3" s="154" t="s">
         <v>323</v>
       </c>
-      <c r="F3" s="166" t="s">
+      <c r="F3" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="157" t="s">
         <v>465</v>
       </c>
-      <c r="H3" s="156" t="s">
+      <c r="H3" s="154" t="s">
         <v>513</v>
       </c>
-      <c r="I3" s="159" t="s">
+      <c r="I3" s="160" t="s">
         <v>515</v>
       </c>
     </row>
@@ -5299,31 +5300,31 @@
       <c r="B4" s="116" t="s">
         <v>286</v>
       </c>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="160"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="161"/>
     </row>
     <row r="5" spans="2:9" ht="51" customHeight="1" thickBot="1">
       <c r="B5" s="117" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="161"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="156"/>
+      <c r="I5" s="162"/>
     </row>
     <row r="6" spans="2:9" ht="62">
       <c r="B6" s="114" t="s">
         <v>467</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="157" t="s">
         <v>154</v>
       </c>
       <c r="D6" s="119" t="s">
@@ -5349,23 +5350,23 @@
       <c r="B7" s="116" t="s">
         <v>468</v>
       </c>
-      <c r="C7" s="154"/>
-      <c r="D7" s="164" t="s">
+      <c r="C7" s="158"/>
+      <c r="D7" s="165" t="s">
         <v>472</v>
       </c>
-      <c r="E7" s="154" t="s">
+      <c r="E7" s="158" t="s">
         <v>323</v>
       </c>
-      <c r="F7" s="154" t="s">
+      <c r="F7" s="158" t="s">
         <v>473</v>
       </c>
-      <c r="G7" s="154" t="s">
+      <c r="G7" s="158" t="s">
         <v>529</v>
       </c>
-      <c r="H7" s="157" t="s">
+      <c r="H7" s="155" t="s">
         <v>517</v>
       </c>
-      <c r="I7" s="162" t="s">
+      <c r="I7" s="163" t="s">
         <v>518</v>
       </c>
     </row>
@@ -5373,37 +5374,37 @@
       <c r="B8" s="116" t="s">
         <v>469</v>
       </c>
-      <c r="C8" s="154"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="154"/>
-      <c r="H8" s="157"/>
-      <c r="I8" s="162"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="155"/>
+      <c r="I8" s="163"/>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="116" t="s">
         <v>470</v>
       </c>
-      <c r="C9" s="154"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="157"/>
-      <c r="I9" s="162"/>
+      <c r="C9" s="158"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="155"/>
+      <c r="I9" s="163"/>
     </row>
     <row r="10" spans="2:9" ht="16" thickBot="1">
       <c r="B10" s="117" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="155"/>
-      <c r="D10" s="165"/>
-      <c r="E10" s="155"/>
-      <c r="F10" s="155"/>
-      <c r="G10" s="155"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="163"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="159"/>
+      <c r="H10" s="156"/>
+      <c r="I10" s="164"/>
     </row>
     <row r="11" spans="2:9" ht="57" customHeight="1">
       <c r="B11" s="114" t="s">
@@ -5412,7 +5413,7 @@
       <c r="C11" s="121" t="s">
         <v>154</v>
       </c>
-      <c r="D11" s="156" t="s">
+      <c r="D11" s="154" t="s">
         <v>475</v>
       </c>
       <c r="E11" s="119" t="s">
@@ -5438,7 +5439,7 @@
       <c r="C12" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="157"/>
+      <c r="D12" s="155"/>
       <c r="E12" s="123" t="s">
         <v>511</v>
       </c>
@@ -5460,7 +5461,7 @@
       <c r="C13" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="157"/>
+      <c r="D13" s="155"/>
       <c r="E13" s="123" t="s">
         <v>480</v>
       </c>
@@ -5482,7 +5483,7 @@
       <c r="C14" t="s">
         <v>154</v>
       </c>
-      <c r="D14" s="157"/>
+      <c r="D14" s="155"/>
       <c r="E14" s="123" t="s">
         <v>482</v>
       </c>
@@ -5504,7 +5505,7 @@
       <c r="C15" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="157"/>
+      <c r="D15" s="155"/>
       <c r="E15" s="123" t="s">
         <v>486</v>
       </c>
@@ -5526,7 +5527,7 @@
       <c r="C16" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="157"/>
+      <c r="D16" s="155"/>
       <c r="E16" s="123" t="s">
         <v>484</v>
       </c>
@@ -5548,7 +5549,7 @@
       <c r="C17" t="s">
         <v>154</v>
       </c>
-      <c r="D17" s="157"/>
+      <c r="D17" s="155"/>
       <c r="E17" s="123" t="s">
         <v>484</v>
       </c>
@@ -5570,7 +5571,7 @@
       <c r="C18" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="157"/>
+      <c r="D18" s="155"/>
       <c r="E18" s="123" t="s">
         <v>489</v>
       </c>
@@ -5594,7 +5595,7 @@
       <c r="C19" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="157"/>
+      <c r="D19" s="155"/>
       <c r="E19" s="123" t="s">
         <v>489</v>
       </c>
@@ -5616,7 +5617,7 @@
       <c r="C20" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="157"/>
+      <c r="D20" s="155"/>
       <c r="E20" s="123" t="s">
         <v>489</v>
       </c>
@@ -5638,7 +5639,7 @@
       <c r="C21" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="157"/>
+      <c r="D21" s="155"/>
       <c r="E21" s="123" t="s">
         <v>489</v>
       </c>
@@ -5660,7 +5661,7 @@
       <c r="C22" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="157"/>
+      <c r="D22" s="155"/>
       <c r="E22" s="123" t="s">
         <v>494</v>
       </c>
@@ -5682,7 +5683,7 @@
       <c r="C23" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="157"/>
+      <c r="D23" s="155"/>
       <c r="E23" s="123" t="s">
         <v>496</v>
       </c>
@@ -5704,7 +5705,7 @@
       <c r="C24" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="157"/>
+      <c r="D24" s="155"/>
       <c r="E24" s="123" t="s">
         <v>498</v>
       </c>
@@ -5726,7 +5727,7 @@
       <c r="C25" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="157"/>
+      <c r="D25" s="155"/>
       <c r="E25" s="123" t="s">
         <v>500</v>
       </c>
@@ -5748,7 +5749,7 @@
       <c r="C26" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="157"/>
+      <c r="D26" s="155"/>
       <c r="E26" s="123" t="s">
         <v>500</v>
       </c>
@@ -5770,7 +5771,7 @@
       <c r="C27" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="157"/>
+      <c r="D27" s="155"/>
       <c r="E27" s="123" t="s">
         <v>503</v>
       </c>
@@ -5792,7 +5793,7 @@
       <c r="C28" t="s">
         <v>154</v>
       </c>
-      <c r="D28" s="157"/>
+      <c r="D28" s="155"/>
       <c r="E28" s="123" t="s">
         <v>505</v>
       </c>
@@ -5814,7 +5815,7 @@
       <c r="C29" t="s">
         <v>154</v>
       </c>
-      <c r="D29" s="157"/>
+      <c r="D29" s="155"/>
       <c r="E29" s="123" t="s">
         <v>507</v>
       </c>
@@ -5836,7 +5837,7 @@
       <c r="C30" s="124" t="s">
         <v>154</v>
       </c>
-      <c r="D30" s="158"/>
+      <c r="D30" s="156"/>
       <c r="E30" s="125" t="s">
         <v>509</v>
       </c>
@@ -5856,13 +5857,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="F7:F10"/>
     <mergeCell ref="G7:G10"/>
     <mergeCell ref="D11:D30"/>
     <mergeCell ref="H3:H5"/>
@@ -5871,6 +5865,13 @@
     <mergeCell ref="I7:I10"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="G3:G5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5878,7 +5879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2064538-98C6-0542-A7AF-646505903CC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56615EF-2DCD-45D0-B202-28F95B04FDC1}">
   <dimension ref="B1:J44"/>
   <sheetFormatPr defaultColWidth="26.33203125" defaultRowHeight="15.5"/>
   <cols>
@@ -5906,7 +5907,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="77.5">
+    <row r="3" spans="2:10" ht="62">
       <c r="B3" s="171" t="s">
         <v>293</v>
       </c>
@@ -6059,7 +6060,7 @@
       </c>
       <c r="G11" s="97"/>
     </row>
-    <row r="12" spans="2:10" ht="46.5">
+    <row r="12" spans="2:10" ht="62">
       <c r="B12" s="169"/>
       <c r="C12" s="96" t="s">
         <v>330</v>
@@ -6529,7 +6530,7 @@
       </c>
       <c r="G39" s="104"/>
     </row>
-    <row r="40" spans="2:7" ht="31">
+    <row r="40" spans="2:7" ht="46.5">
       <c r="B40" s="168"/>
       <c r="C40" s="100" t="s">
         <v>430</v>
@@ -6630,6 +6631,758 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2064538-98C6-0542-A7AF-646505903CC4}">
+  <dimension ref="B1:J44"/>
+  <sheetFormatPr defaultColWidth="26.33203125" defaultRowHeight="15.5"/>
+  <cols>
+    <col min="7" max="7" width="26.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" ht="16" thickBot="1"/>
+    <row r="2" spans="2:10" ht="25" customHeight="1" thickBot="1">
+      <c r="B2" s="93" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>533</v>
+      </c>
+      <c r="D2" s="94" t="s">
+        <v>289</v>
+      </c>
+      <c r="E2" s="94" t="s">
+        <v>290</v>
+      </c>
+      <c r="F2" s="94" t="s">
+        <v>291</v>
+      </c>
+      <c r="G2" s="95" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="77.5">
+      <c r="B3" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="96" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" s="96" t="s">
+        <v>295</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>296</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>297</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="112" customHeight="1">
+      <c r="B4" s="169"/>
+      <c r="C4" s="96" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="96" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="96" t="s">
+        <v>296</v>
+      </c>
+      <c r="F4" s="96" t="s">
+        <v>301</v>
+      </c>
+      <c r="G4" s="97"/>
+    </row>
+    <row r="5" spans="2:10" ht="124">
+      <c r="B5" s="169"/>
+      <c r="C5" s="96" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" s="96" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="96" t="s">
+        <v>304</v>
+      </c>
+      <c r="F5" s="96" t="s">
+        <v>305</v>
+      </c>
+      <c r="G5" s="97" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="124">
+      <c r="B6" s="169"/>
+      <c r="C6" s="96" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="96" t="s">
+        <v>304</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="97" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="31">
+      <c r="B7" s="169"/>
+      <c r="C7" s="98" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" s="98" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="99"/>
+    </row>
+    <row r="8" spans="2:10" ht="31">
+      <c r="B8" s="169"/>
+      <c r="C8" s="98" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="E8" s="98" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="98"/>
+      <c r="G8" s="99"/>
+      <c r="J8" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="46.5">
+      <c r="B9" s="172" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="100" t="s">
+        <v>317</v>
+      </c>
+      <c r="D9" s="101" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="101" t="s">
+        <v>319</v>
+      </c>
+      <c r="F9" s="100" t="s">
+        <v>320</v>
+      </c>
+      <c r="G9" s="102"/>
+    </row>
+    <row r="10" spans="2:10" ht="31">
+      <c r="B10" s="172"/>
+      <c r="C10" s="100" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="101" t="s">
+        <v>322</v>
+      </c>
+      <c r="E10" s="101" t="s">
+        <v>323</v>
+      </c>
+      <c r="F10" s="100" t="s">
+        <v>324</v>
+      </c>
+      <c r="G10" s="102"/>
+    </row>
+    <row r="11" spans="2:10" ht="77.5">
+      <c r="B11" s="169" t="s">
+        <v>325</v>
+      </c>
+      <c r="C11" s="96" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>327</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>328</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>329</v>
+      </c>
+      <c r="G11" s="97"/>
+    </row>
+    <row r="12" spans="2:10" ht="46.5">
+      <c r="B12" s="169"/>
+      <c r="C12" s="96" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" s="96" t="s">
+        <v>332</v>
+      </c>
+      <c r="F12" s="96" t="s">
+        <v>333</v>
+      </c>
+      <c r="G12" s="97"/>
+    </row>
+    <row r="13" spans="2:10" ht="31">
+      <c r="B13" s="169"/>
+      <c r="C13" s="96" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>335</v>
+      </c>
+      <c r="E13" s="96" t="s">
+        <v>336</v>
+      </c>
+      <c r="F13" s="96"/>
+      <c r="G13" s="97"/>
+    </row>
+    <row r="14" spans="2:10" ht="93">
+      <c r="B14" s="168" t="s">
+        <v>337</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="100" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="103" t="s">
+        <v>340</v>
+      </c>
+      <c r="F14" s="100" t="s">
+        <v>341</v>
+      </c>
+      <c r="G14" s="104"/>
+    </row>
+    <row r="15" spans="2:10" ht="46.5">
+      <c r="B15" s="168"/>
+      <c r="C15" s="100" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" s="100" t="s">
+        <v>343</v>
+      </c>
+      <c r="E15" s="100" t="s">
+        <v>344</v>
+      </c>
+      <c r="F15" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="104" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="62">
+      <c r="B16" s="168"/>
+      <c r="C16" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="100" t="s">
+        <v>348</v>
+      </c>
+      <c r="E16" s="100" t="s">
+        <v>349</v>
+      </c>
+      <c r="F16" s="100" t="s">
+        <v>350</v>
+      </c>
+      <c r="G16" s="104"/>
+    </row>
+    <row r="17" spans="2:7" ht="46.5">
+      <c r="B17" s="168"/>
+      <c r="C17" s="100" t="s">
+        <v>351</v>
+      </c>
+      <c r="D17" s="100" t="s">
+        <v>352</v>
+      </c>
+      <c r="E17" s="100" t="s">
+        <v>353</v>
+      </c>
+      <c r="F17" s="100" t="s">
+        <v>354</v>
+      </c>
+      <c r="G17" s="104"/>
+    </row>
+    <row r="18" spans="2:7" ht="31">
+      <c r="B18" s="168"/>
+      <c r="C18" s="100" t="s">
+        <v>355</v>
+      </c>
+      <c r="D18" s="100" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" s="100" t="s">
+        <v>357</v>
+      </c>
+      <c r="F18" s="100" t="s">
+        <v>358</v>
+      </c>
+      <c r="G18" s="104"/>
+    </row>
+    <row r="19" spans="2:7" ht="62">
+      <c r="B19" s="168"/>
+      <c r="C19" s="100" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" s="100" t="s">
+        <v>360</v>
+      </c>
+      <c r="E19" s="100" t="s">
+        <v>361</v>
+      </c>
+      <c r="F19" s="100" t="s">
+        <v>362</v>
+      </c>
+      <c r="G19" s="104"/>
+    </row>
+    <row r="20" spans="2:7" ht="31">
+      <c r="B20" s="168"/>
+      <c r="C20" s="100" t="s">
+        <v>363</v>
+      </c>
+      <c r="D20" s="100" t="s">
+        <v>364</v>
+      </c>
+      <c r="E20" s="100" t="s">
+        <v>365</v>
+      </c>
+      <c r="F20" s="100" t="s">
+        <v>366</v>
+      </c>
+      <c r="G20" s="104"/>
+    </row>
+    <row r="21" spans="2:7" ht="31">
+      <c r="B21" s="168"/>
+      <c r="C21" s="100" t="s">
+        <v>367</v>
+      </c>
+      <c r="D21" s="100" t="s">
+        <v>368</v>
+      </c>
+      <c r="E21" s="100" t="s">
+        <v>369</v>
+      </c>
+      <c r="F21" s="100" t="s">
+        <v>366</v>
+      </c>
+      <c r="G21" s="104"/>
+    </row>
+    <row r="22" spans="2:7" ht="46.5">
+      <c r="B22" s="168"/>
+      <c r="C22" s="100" t="s">
+        <v>370</v>
+      </c>
+      <c r="D22" s="100" t="s">
+        <v>371</v>
+      </c>
+      <c r="E22" s="100" t="s">
+        <v>372</v>
+      </c>
+      <c r="F22" s="100" t="s">
+        <v>373</v>
+      </c>
+      <c r="G22" s="104"/>
+    </row>
+    <row r="23" spans="2:7" ht="46.5">
+      <c r="B23" s="168"/>
+      <c r="C23" s="100" t="s">
+        <v>374</v>
+      </c>
+      <c r="D23" s="100" t="s">
+        <v>375</v>
+      </c>
+      <c r="E23" s="100" t="s">
+        <v>323</v>
+      </c>
+      <c r="F23" s="100" t="s">
+        <v>376</v>
+      </c>
+      <c r="G23" s="104"/>
+    </row>
+    <row r="24" spans="2:7" ht="46.5">
+      <c r="B24" s="169" t="s">
+        <v>377</v>
+      </c>
+      <c r="C24" s="96" t="s">
+        <v>378</v>
+      </c>
+      <c r="D24" s="96" t="s">
+        <v>379</v>
+      </c>
+      <c r="E24" s="96" t="s">
+        <v>380</v>
+      </c>
+      <c r="F24" s="96" t="s">
+        <v>381</v>
+      </c>
+      <c r="G24" s="97" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="46.5">
+      <c r="B25" s="169"/>
+      <c r="C25" s="96" t="s">
+        <v>383</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="E25" s="96" t="s">
+        <v>385</v>
+      </c>
+      <c r="F25" s="96" t="s">
+        <v>381</v>
+      </c>
+      <c r="G25" s="97" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="62">
+      <c r="B26" s="169"/>
+      <c r="C26" s="96" t="s">
+        <v>386</v>
+      </c>
+      <c r="D26" s="96" t="s">
+        <v>387</v>
+      </c>
+      <c r="E26" s="96" t="s">
+        <v>388</v>
+      </c>
+      <c r="F26" s="96" t="s">
+        <v>381</v>
+      </c>
+      <c r="G26" s="97" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="62">
+      <c r="B27" s="169"/>
+      <c r="C27" s="96" t="s">
+        <v>389</v>
+      </c>
+      <c r="D27" s="96" t="s">
+        <v>390</v>
+      </c>
+      <c r="E27" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="F27" s="96" t="s">
+        <v>381</v>
+      </c>
+      <c r="G27" s="97" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="31">
+      <c r="B28" s="169"/>
+      <c r="C28" s="96" t="s">
+        <v>392</v>
+      </c>
+      <c r="D28" s="96" t="s">
+        <v>393</v>
+      </c>
+      <c r="E28" s="96" t="s">
+        <v>394</v>
+      </c>
+      <c r="F28" s="96" t="s">
+        <v>381</v>
+      </c>
+      <c r="G28" s="97" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="169"/>
+      <c r="C29" s="98" t="s">
+        <v>395</v>
+      </c>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="99"/>
+    </row>
+    <row r="30" spans="2:7" ht="62">
+      <c r="B30" s="168" t="s">
+        <v>396</v>
+      </c>
+      <c r="C30" s="100" t="s">
+        <v>378</v>
+      </c>
+      <c r="D30" s="100" t="s">
+        <v>397</v>
+      </c>
+      <c r="E30" s="100" t="s">
+        <v>398</v>
+      </c>
+      <c r="F30" s="100" t="s">
+        <v>399</v>
+      </c>
+      <c r="G30" s="102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="62">
+      <c r="B31" s="168"/>
+      <c r="C31" s="100" t="s">
+        <v>383</v>
+      </c>
+      <c r="D31" s="100" t="s">
+        <v>401</v>
+      </c>
+      <c r="E31" s="100" t="s">
+        <v>402</v>
+      </c>
+      <c r="F31" s="100" t="s">
+        <v>399</v>
+      </c>
+      <c r="G31" s="102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="62">
+      <c r="B32" s="168"/>
+      <c r="C32" s="100" t="s">
+        <v>386</v>
+      </c>
+      <c r="D32" s="100" t="s">
+        <v>403</v>
+      </c>
+      <c r="E32" s="100" t="s">
+        <v>404</v>
+      </c>
+      <c r="F32" s="100" t="s">
+        <v>399</v>
+      </c>
+      <c r="G32" s="102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="62">
+      <c r="B33" s="168"/>
+      <c r="C33" s="100" t="s">
+        <v>389</v>
+      </c>
+      <c r="D33" s="100" t="s">
+        <v>405</v>
+      </c>
+      <c r="E33" s="100" t="s">
+        <v>406</v>
+      </c>
+      <c r="F33" s="100" t="s">
+        <v>399</v>
+      </c>
+      <c r="G33" s="102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="62">
+      <c r="B34" s="168"/>
+      <c r="C34" s="100" t="s">
+        <v>392</v>
+      </c>
+      <c r="D34" s="100" t="s">
+        <v>407</v>
+      </c>
+      <c r="E34" s="100" t="s">
+        <v>408</v>
+      </c>
+      <c r="F34" s="100" t="s">
+        <v>399</v>
+      </c>
+      <c r="G34" s="102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="77.5">
+      <c r="B35" s="167" t="s">
+        <v>409</v>
+      </c>
+      <c r="C35" s="96" t="s">
+        <v>410</v>
+      </c>
+      <c r="D35" s="96" t="s">
+        <v>411</v>
+      </c>
+      <c r="E35" s="96" t="s">
+        <v>412</v>
+      </c>
+      <c r="F35" s="96" t="s">
+        <v>413</v>
+      </c>
+      <c r="G35" s="105"/>
+    </row>
+    <row r="36" spans="2:7" ht="31">
+      <c r="B36" s="167"/>
+      <c r="C36" s="96" t="s">
+        <v>414</v>
+      </c>
+      <c r="D36" s="96" t="s">
+        <v>415</v>
+      </c>
+      <c r="E36" s="96" t="s">
+        <v>416</v>
+      </c>
+      <c r="F36" s="96" t="s">
+        <v>417</v>
+      </c>
+      <c r="G36" s="105"/>
+    </row>
+    <row r="37" spans="2:7" ht="46.5">
+      <c r="B37" s="167"/>
+      <c r="C37" s="96" t="s">
+        <v>418</v>
+      </c>
+      <c r="D37" s="96" t="s">
+        <v>419</v>
+      </c>
+      <c r="E37" s="106"/>
+      <c r="F37" s="96" t="s">
+        <v>420</v>
+      </c>
+      <c r="G37" s="105"/>
+    </row>
+    <row r="38" spans="2:7" ht="31">
+      <c r="B38" s="168" t="s">
+        <v>421</v>
+      </c>
+      <c r="C38" s="100" t="s">
+        <v>422</v>
+      </c>
+      <c r="D38" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="E38" s="100" t="s">
+        <v>424</v>
+      </c>
+      <c r="F38" s="100" t="s">
+        <v>425</v>
+      </c>
+      <c r="G38" s="104"/>
+    </row>
+    <row r="39" spans="2:7" ht="62">
+      <c r="B39" s="168"/>
+      <c r="C39" s="100" t="s">
+        <v>426</v>
+      </c>
+      <c r="D39" s="100" t="s">
+        <v>427</v>
+      </c>
+      <c r="E39" s="100" t="s">
+        <v>428</v>
+      </c>
+      <c r="F39" s="100" t="s">
+        <v>429</v>
+      </c>
+      <c r="G39" s="104"/>
+    </row>
+    <row r="40" spans="2:7" ht="31">
+      <c r="B40" s="168"/>
+      <c r="C40" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="D40" s="107" t="s">
+        <v>431</v>
+      </c>
+      <c r="E40" s="100" t="s">
+        <v>432</v>
+      </c>
+      <c r="F40" s="100" t="s">
+        <v>433</v>
+      </c>
+      <c r="G40" s="104"/>
+    </row>
+    <row r="41" spans="2:7" ht="77.5">
+      <c r="B41" s="168"/>
+      <c r="C41" s="100" t="s">
+        <v>434</v>
+      </c>
+      <c r="D41" s="100" t="s">
+        <v>435</v>
+      </c>
+      <c r="E41" s="100" t="s">
+        <v>436</v>
+      </c>
+      <c r="F41" s="100" t="s">
+        <v>437</v>
+      </c>
+      <c r="G41" s="104"/>
+    </row>
+    <row r="42" spans="2:7" ht="46.5">
+      <c r="B42" s="169" t="s">
+        <v>438</v>
+      </c>
+      <c r="C42" s="96" t="s">
+        <v>439</v>
+      </c>
+      <c r="D42" s="96" t="s">
+        <v>440</v>
+      </c>
+      <c r="E42" s="106"/>
+      <c r="F42" s="96" t="s">
+        <v>441</v>
+      </c>
+      <c r="G42" s="105" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="46.5">
+      <c r="B43" s="169"/>
+      <c r="C43" s="96" t="s">
+        <v>443</v>
+      </c>
+      <c r="D43" s="96" t="s">
+        <v>444</v>
+      </c>
+      <c r="E43" s="96" t="s">
+        <v>440</v>
+      </c>
+      <c r="F43" s="96" t="s">
+        <v>445</v>
+      </c>
+      <c r="G43" s="105" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="31.5" thickBot="1">
+      <c r="B44" s="170"/>
+      <c r="C44" s="108" t="s">
+        <v>447</v>
+      </c>
+      <c r="D44" s="108" t="s">
+        <v>448</v>
+      </c>
+      <c r="E44" s="108" t="s">
+        <v>449</v>
+      </c>
+      <c r="F44" s="108" t="s">
+        <v>450</v>
+      </c>
+      <c r="G44" s="109"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B23"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="B30:B34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5D6BDA-CD8A-F745-9432-929ADAAADE49}">
   <dimension ref="B1:G10"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
@@ -6750,7 +7503,7 @@
       </c>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="2:7" ht="170.5">
+    <row r="8" spans="2:7" ht="186">
       <c r="B8" s="32" t="s">
         <v>116</v>
       </c>
